--- a/Project-Plan-Gantt.xlsx
+++ b/Project-Plan-Gantt.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="173">
   <si>
-    <t xml:space="preserve">MWD Enterprise Cybersecurity Program — 12-Month Project Plan (Gantt Chart)</t>
+    <t xml:space="preserve">Water District Enterprise Cybersecurity Program — 12-Month Project Plan (Gantt Chart)</t>
   </si>
   <si>
     <t xml:space="preserve">Project Start Date (edit this cell to reschedule the entire plan):</t>
@@ -103,255 +103,255 @@
     <t xml:space="preserve">Charter approved by executive sponsor</t>
   </si>
   <si>
-    <t xml:space="preserve">MDR/24x7 SOC augmentation - procurement</t>
+    <t xml:space="preserve">SOC 24x7 shift-handoff and escalation procedure review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documented shift-handoff/escalation runbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewed and validated across all 3 SOC shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOC workflow integration - align CrowdStrike/QRadar alert routing with 3-shift rotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity Manager, SOC Analysts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alert routing/escalation matrix updated for 3-shift SOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero alert routing gaps confirmed across shift handoffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup immutability assessment and remediation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immutable/air-gapped backup confirmed for Tier-1 systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object-lock or air-gap verified on backup repository</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security awareness training platform deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRC Consultants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awareness platform live org-wide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% of users enrolled; first phishing simulation scheduled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT monitoring platform - SIEM integration and connector feasibility assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISO, Network Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration approach and connector selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feasibility confirmed; integration project chartered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm M365 E5/Entra ID P2 licensing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licensing confirmation memo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licensing gaps identified and remediated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enforce phishing-resistant MFA for privileged accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFA enforced for all privileged accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% privileged account MFA coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced email security pilot (Proofpoint/Mimecast/Abnormal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 - Identity &amp; Data Protection (M2-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email security pilot live for high-risk mailboxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot mailboxes protected; false-positive rate acceptable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLP policy design (Microsoft Purview)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRC Consultants, Cybersecurity Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLP policy draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy reviewed and approved by data owners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secrets management pilot (Vault/CyberArk Conjur)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secrets vaulting pilot for top 10 applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot applications no longer use hardcoded credentials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced email security full rollout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email security live org-wide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% mailbox coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLP policy rollout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLP enforced across email/SharePoint/Teams/endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLP incidents logged and triaged in SIEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAM depth enhancement (JIT, session recording)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enhanced PAM configuration live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% privileged sessions recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnerability management platform deployment (Tenable/Rapid7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity Manager, Network Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VM platform deployed and scanning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full IT asset scan coverage achieved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnerability management SLA policy finalization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISO, GRC Consultants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signed VM SLA policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy signed by executive leadership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First full vulnerability baseline report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline vulnerability report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report delivered to CISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOAR platform deployment (Cortex XSOAR/QRadar SOAR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2 - Detection &amp; Response (M4-6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOC Analysts, Cybersecurity Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOAR live and integrated with QRadar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOAR ingesting SIEM alerts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOAR playbook development (phishing/isolation/IOC blocklist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOC Analysts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 production playbooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playbooks handling live Tier-1 alerts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threat intelligence platform integration (WaterISAC + commercial feed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIP integrated into QRadar/SOAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOC feed actively enriching alerts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASB/SSPM deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS posture monitoring live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline SaaS posture report delivered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack surface management tool deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External ASM baseline established</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline external exposure report delivered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLP rollout completion beyond pilot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLP fully enforced org-wide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All defined data categories covered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR playbook quarterly/annual review and update (formalize recurring cadence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated IR playbook plus documented review cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playbook reviewed and updated; cadence approved by CISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retained DFIR firm contract</t>
   </si>
   <si>
     <t xml:space="preserve">CISO</t>
   </si>
   <si>
-    <t xml:space="preserve">Signed MDR contract (Falcon Complete/OverWatch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contract executed; onboarding scheduled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDR onboarding and integration with CrowdStrike/QRadar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersecurity Manager, Threat Analysts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24x7 monitoring live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDR provider actively triaging alerts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backup immutability assessment and remediation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immutable/air-gapped backup confirmed for Tier-1 systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Object-lock or air-gap verified on backup repository</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security awareness training platform deployment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRC Consultants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awareness platform live org-wide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100% of users enrolled; first phishing simulation scheduled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT/ICS security vendor assessment (Claroty/Dragos/Nozomi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISO, Network Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor shortlist and selection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor selected; SOW drafted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm M365 E5/Entra ID P2 licensing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersecurity Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licensing confirmation memo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licensing gaps identified and remediated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enforce phishing-resistant MFA for privileged accounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFA enforced for all privileged accounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100% privileged account MFA coverage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced email security pilot (Proofpoint/Mimecast/Abnormal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1 - Identity &amp; Data Protection (M2-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email security pilot live for high-risk mailboxes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilot mailboxes protected; false-positive rate acceptable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLP policy design (Microsoft Purview)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRC Consultants, Cybersecurity Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLP policy draft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy reviewed and approved by data owners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secrets management pilot (Vault/CyberArk Conjur)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secrets vaulting pilot for top 10 applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilot applications no longer use hardcoded credentials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced email security full rollout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email security live org-wide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100% mailbox coverage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLP policy rollout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLP enforced across email/SharePoint/Teams/endpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLP incidents logged and triaged in SIEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAM depth enhancement (JIT, session recording)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enhanced PAM configuration live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100% privileged sessions recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vulnerability management platform deployment (Tenable/Rapid7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersecurity Manager, Network Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VM platform deployed and scanning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full IT asset scan coverage achieved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vulnerability management SLA policy finalization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISO, GRC Consultants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signed VM SLA policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy signed by executive leadership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First full vulnerability baseline report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline vulnerability report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report delivered to CISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOAR platform deployment (Cortex XSOAR/QRadar SOAR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2 - Detection &amp; Response (M4-6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threat Analysts, Cybersecurity Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOAR live and integrated with QRadar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOAR ingesting SIEM alerts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOAR playbook development (phishing/isolation/IOC blocklist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threat Analysts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 production playbooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playbooks handling live Tier-1 alerts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threat intelligence platform integration (WaterISAC + commercial feed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIP integrated into QRadar/SOAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOC feed actively enriching alerts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASB/SSPM deployment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS posture monitoring live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline SaaS posture report delivered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack surface management tool deployment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External ASM baseline established</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline external exposure report delivered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLP rollout completion beyond pilot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLP fully enforced org-wide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All defined data categories covered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IR plan and runbook formalization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signed IR plan and runbooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IR plan approved by executive leadership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retained DFIR firm contract</t>
-  </si>
-  <si>
     <t xml:space="preserve">Signed DFIR retainer contract</t>
   </si>
   <si>
@@ -361,7 +361,7 @@
     <t xml:space="preserve">First tabletop exercise (ransomware scenario)</t>
   </si>
   <si>
-    <t xml:space="preserve">CISO, Cybersecurity Manager, Threat Analysts</t>
+    <t xml:space="preserve">CISO, Cybersecurity Manager, SOC Analysts</t>
   </si>
   <si>
     <t xml:space="preserve">Tabletop after-action report</t>
@@ -370,40 +370,40 @@
     <t xml:space="preserve">Findings documented and remediation tracked</t>
   </si>
   <si>
-    <t xml:space="preserve">OT/ICS monitoring platform deployment - wave 1 sites</t>
+    <t xml:space="preserve">OT monitoring platform integration with QRadar SIEM (wave 1 sites)</t>
   </si>
   <si>
     <t xml:space="preserve">P3 - Cloud &amp; OT Security (M7-9)</t>
   </si>
   <si>
-    <t xml:space="preserve">Network Specialist, Threat Analysts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT monitoring live at wave 1 facilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT asset inventory v1 delivered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT/ICS alert integration into QRadar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT alerts visible in SIEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT alerts triaged through existing SOC workflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT/OT segmentation project (Panorama/ISE boundary enforcement)</t>
+    <t xml:space="preserve">Network Specialist, SOC Analysts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT alerts flowing into QRadar for wave 1 sites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT alert volume/quality validated by SOC; asset inventory reconciled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT alert triage playbook and SOC analyst training (wave 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT triage playbook and trained SOC rotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOC analysts triaging OT alerts to defined SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT/OT segmentation validation and hardening (Panorama/ISE boundary)</t>
   </si>
   <si>
     <t xml:space="preserve">Network Specialist, CISO</t>
   </si>
   <si>
-    <t xml:space="preserve">Segmentation implemented at wave 1 sites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No direct OT-to-internet paths; segmentation validated</t>
+    <t xml:space="preserve">Segmentation validated and hardened at wave 1 sites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No direct OT-to-internet paths confirmed; segmentation tested</t>
   </si>
   <si>
     <t xml:space="preserve">Vendor remote access brokered through PAM</t>
@@ -424,19 +424,19 @@
     <t xml:space="preserve">Misconfigurations tracked and remediated</t>
   </si>
   <si>
-    <t xml:space="preserve">PKI/certificate lifecycle management deployment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certificate inventory and expiry alerting live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zero unplanned cert-expiry outages</t>
+    <t xml:space="preserve">Yubico PKI/certificate lifecycle scope review and SIEM expiry-alert integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificate scope confirmed; expiry alerts integrated into QRadar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full certificate inventory reconciled; zero unplanned cert-expiry outages</t>
   </si>
   <si>
     <t xml:space="preserve">Purple team exercise</t>
   </si>
   <si>
-    <t xml:space="preserve">CISO, Threat Analysts</t>
+    <t xml:space="preserve">CISO, SOC Analysts</t>
   </si>
   <si>
     <t xml:space="preserve">Purple team after-action report</t>
@@ -1101,7 +1101,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1114,7 +1114,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="8" min="8" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="13" style="0" width="4.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="13" style="0" width="4.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1143,7 +1143,6 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -1277,10 +1276,6 @@
         <f aca="false">EDATE($G$2,COLUMN()-COLUMN($M$4))</f>
         <v>46541</v>
       </c>
-      <c r="X4" s="12" t="n">
-        <f aca="false">EDATE($G$2,COLUMN()-COLUMN($M$4))</f>
-        <v>46571</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="n">
@@ -1549,13 +1544,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="H11" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="I11" s="16" t="n">
         <f aca="false">IF(AND(E11="",L11=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E11,$A$5:$A$47,0)),0),L11),1))</f>
@@ -1579,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>22</v>
@@ -1591,13 +1586,13 @@
         <v>7</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="I12" s="16" t="n">
         <f aca="false">IF(AND(E12="",L12=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E12,$A$5:$A$47,0)),0),L12),1))</f>
@@ -1621,10 +1616,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>54</v>
       </c>
       <c r="D13" s="13" t="n">
         <v>15</v>
@@ -1636,10 +1631,10 @@
         <v>35</v>
       </c>
       <c r="G13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="14" t="s">
         <v>55</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>56</v>
       </c>
       <c r="I13" s="16" t="n">
         <f aca="false">IF(AND(E13="",L13=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E13,$A$5:$A$47,0)),0),L13),1))</f>
@@ -1663,10 +1658,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>15</v>
@@ -1675,13 +1670,13 @@
         <v>7</v>
       </c>
       <c r="F14" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="H14" s="14" t="s">
         <v>59</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>60</v>
       </c>
       <c r="I14" s="16" t="n">
         <f aca="false">IF(AND(E14="",L14=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E14,$A$5:$A$47,0)),0),L14),1))</f>
@@ -1705,10 +1700,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>15</v>
@@ -1720,10 +1715,10 @@
         <v>35</v>
       </c>
       <c r="G15" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="14" t="s">
         <v>62</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>63</v>
       </c>
       <c r="I15" s="16" t="n">
         <f aca="false">IF(AND(E15="",L15=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E15,$A$5:$A$47,0)),0),L15),1))</f>
@@ -1747,10 +1742,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>10</v>
@@ -1762,10 +1757,10 @@
         <v>35</v>
       </c>
       <c r="G16" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>66</v>
       </c>
       <c r="I16" s="16" t="n">
         <f aca="false">IF(AND(E16="",L16=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E16,$A$5:$A$47,0)),0),L16),1))</f>
@@ -1789,10 +1784,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="13" t="n">
         <v>15</v>
@@ -1801,13 +1796,13 @@
         <v>10</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="I17" s="16" t="n">
         <f aca="false">IF(AND(E17="",L17=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E17,$A$5:$A$47,0)),0),L17),1))</f>
@@ -1831,10 +1826,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" s="13" t="n">
         <v>20</v>
@@ -1843,13 +1838,13 @@
         <v>8</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G18" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="14" t="s">
         <v>71</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>72</v>
       </c>
       <c r="I18" s="16" t="n">
         <f aca="false">IF(AND(E18="",L18=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E18,$A$5:$A$47,0)),0),L18),1))</f>
@@ -1873,10 +1868,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="13" t="n">
         <v>15</v>
@@ -1885,13 +1880,13 @@
         <v>7</v>
       </c>
       <c r="F19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="H19" s="14" t="s">
         <v>75</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>76</v>
       </c>
       <c r="I19" s="16" t="n">
         <f aca="false">IF(AND(E19="",L19=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E19,$A$5:$A$47,0)),0),L19),1))</f>
@@ -1915,10 +1910,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="13" t="n">
         <v>10</v>
@@ -1927,13 +1922,13 @@
         <v>15</v>
       </c>
       <c r="F20" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="H20" s="14" t="s">
         <v>79</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>80</v>
       </c>
       <c r="I20" s="16" t="n">
         <f aca="false">IF(AND(E20="",L20=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E20,$A$5:$A$47,0)),0),L20),1))</f>
@@ -1957,10 +1952,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="13" t="n">
         <v>5</v>
@@ -1969,13 +1964,13 @@
         <v>15</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G21" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="14" t="s">
         <v>82</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>83</v>
       </c>
       <c r="I21" s="16" t="n">
         <f aca="false">IF(AND(E21="",L21=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E21,$A$5:$A$47,0)),0),L21),1))</f>
@@ -1999,10 +1994,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>84</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="D22" s="13" t="n">
         <v>20</v>
@@ -2011,13 +2006,13 @@
         <v>3</v>
       </c>
       <c r="F22" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="H22" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">IF(AND(E22="",L22=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E22,$A$5:$A$47,0)),0),L22),1))</f>
@@ -2041,10 +2036,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D23" s="13" t="n">
         <v>15</v>
@@ -2053,13 +2048,13 @@
         <v>18</v>
       </c>
       <c r="F23" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="H23" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>92</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">IF(AND(E23="",L23=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E23,$A$5:$A$47,0)),0),L23),1))</f>
@@ -2083,10 +2078,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" s="13" t="n">
         <v>15</v>
@@ -2095,13 +2090,13 @@
         <v>18</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G24" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>95</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">IF(AND(E24="",L24=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E24,$A$5:$A$47,0)),0),L24),1))</f>
@@ -2125,10 +2120,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="13" t="n">
         <v>15</v>
@@ -2140,10 +2135,10 @@
         <v>35</v>
       </c>
       <c r="G25" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>98</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">IF(AND(E25="",L25=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E25,$A$5:$A$47,0)),0),L25),1))</f>
@@ -2167,10 +2162,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" s="13" t="n">
         <v>10</v>
@@ -2182,10 +2177,10 @@
         <v>35</v>
       </c>
       <c r="G26" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="14" t="s">
         <v>100</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>101</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">IF(AND(E26="",L26=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E26,$A$5:$A$47,0)),0),L26),1))</f>
@@ -2209,10 +2204,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D27" s="13" t="n">
         <v>10</v>
@@ -2221,13 +2216,13 @@
         <v>13</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G27" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" s="14" t="s">
         <v>103</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>104</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">IF(AND(E27="",L27=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E27,$A$5:$A$47,0)),0),L27),1))</f>
@@ -2251,10 +2246,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D28" s="13" t="n">
         <v>15</v>
@@ -2266,10 +2261,10 @@
         <v>23</v>
       </c>
       <c r="G28" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>107</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">IF(AND(E28="",L28=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E28,$A$5:$A$47,0)),0),L28),1))</f>
@@ -2293,10 +2288,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D29" s="13" t="n">
         <v>15</v>
@@ -2305,7 +2300,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>109</v>
@@ -2338,7 +2333,7 @@
         <v>111</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D30" s="13" t="n">
         <v>5</v>
@@ -2383,7 +2378,7 @@
         <v>116</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>6</v>
@@ -2403,7 +2398,7 @@
       </c>
       <c r="J31" s="16" t="n">
         <f aca="false">WORKDAY(I31,D31-1)</f>
-        <v>46395</v>
+        <v>46381</v>
       </c>
       <c r="K31" s="13" t="n">
         <f aca="false">MATCH(C31,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2431,7 +2426,7 @@
         <v>27</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G32" s="14" t="s">
         <v>121</v>
@@ -2441,11 +2436,11 @@
       </c>
       <c r="I32" s="16" t="n">
         <f aca="false">IF(AND(E32="",L32=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E32,$A$5:$A$47,0)),0),L32),1))</f>
-        <v>46398</v>
+        <v>46384</v>
       </c>
       <c r="J32" s="16" t="n">
         <f aca="false">WORKDAY(I32,D32-1)</f>
-        <v>46409</v>
+        <v>46395</v>
       </c>
       <c r="K32" s="13" t="n">
         <f aca="false">MATCH(C32,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2467,7 +2462,7 @@
         <v>116</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>27</v>
@@ -2483,11 +2478,11 @@
       </c>
       <c r="I33" s="16" t="n">
         <f aca="false">IF(AND(E33="",L33=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E33,$A$5:$A$47,0)),0),L33),1))</f>
-        <v>46398</v>
+        <v>46384</v>
       </c>
       <c r="J33" s="16" t="n">
         <f aca="false">WORKDAY(I33,D33-1)</f>
-        <v>46430</v>
+        <v>46402</v>
       </c>
       <c r="K33" s="13" t="n">
         <f aca="false">MATCH(C33,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2525,11 +2520,11 @@
       </c>
       <c r="I34" s="16" t="n">
         <f aca="false">IF(AND(E34="",L34=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E34,$A$5:$A$47,0)),0),L34),1))</f>
-        <v>46433</v>
+        <v>46405</v>
       </c>
       <c r="J34" s="16" t="n">
         <f aca="false">WORKDAY(I34,D34-1)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
       <c r="K34" s="13" t="n">
         <f aca="false">MATCH(C34,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2593,7 +2588,7 @@
         <v>116</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E36" s="13" t="n">
         <v>1</v>
@@ -2613,7 +2608,7 @@
       </c>
       <c r="J36" s="16" t="n">
         <f aca="false">WORKDAY(I36,D36-1)</f>
-        <v>46381</v>
+        <v>46374</v>
       </c>
       <c r="K36" s="13" t="n">
         <f aca="false">MATCH(C36,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2693,11 +2688,11 @@
       </c>
       <c r="I38" s="16" t="n">
         <f aca="false">IF(AND(E38="",L38=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E38,$A$5:$A$47,0)),0),L38),1))</f>
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="J38" s="16" t="n">
         <f aca="false">WORKDAY(I38,D38-1)</f>
-        <v>46465</v>
+        <v>46437</v>
       </c>
       <c r="K38" s="13" t="n">
         <f aca="false">MATCH(C38,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="L38" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2735,11 +2730,11 @@
       </c>
       <c r="I39" s="16" t="n">
         <f aca="false">IF(AND(E39="",L39=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E39,$A$5:$A$47,0)),0),L39),1))</f>
-        <v>46468</v>
+        <v>46440</v>
       </c>
       <c r="J39" s="16" t="n">
         <f aca="false">WORKDAY(I39,D39-1)</f>
-        <v>46486</v>
+        <v>46458</v>
       </c>
       <c r="K39" s="13" t="n">
         <f aca="false">MATCH(C39,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2747,7 +2742,7 @@
       </c>
       <c r="L39" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2777,11 +2772,11 @@
       </c>
       <c r="I40" s="16" t="n">
         <f aca="false">IF(AND(E40="",L40=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E40,$A$5:$A$47,0)),0),L40),1))</f>
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="J40" s="16" t="n">
         <f aca="false">WORKDAY(I40,D40-1)</f>
-        <v>46458</v>
+        <v>46430</v>
       </c>
       <c r="K40" s="13" t="n">
         <f aca="false">MATCH(C40,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2789,7 +2784,7 @@
       </c>
       <c r="L40" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2819,11 +2814,11 @@
       </c>
       <c r="I41" s="16" t="n">
         <f aca="false">IF(AND(E41="",L41=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E41,$A$5:$A$47,0)),0),L41),1))</f>
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="J41" s="16" t="n">
         <f aca="false">WORKDAY(I41,D41-1)</f>
-        <v>46465</v>
+        <v>46437</v>
       </c>
       <c r="K41" s="13" t="n">
         <f aca="false">MATCH(C41,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2831,7 +2826,7 @@
       </c>
       <c r="L41" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2861,11 +2856,11 @@
       </c>
       <c r="I42" s="16" t="n">
         <f aca="false">IF(AND(E42="",L42=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E42,$A$5:$A$47,0)),0),L42),1))</f>
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="J42" s="16" t="n">
         <f aca="false">WORKDAY(I42,D42-1)</f>
-        <v>46458</v>
+        <v>46430</v>
       </c>
       <c r="K42" s="13" t="n">
         <f aca="false">MATCH(C42,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2873,7 +2868,7 @@
       </c>
       <c r="L42" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2903,11 +2898,11 @@
       </c>
       <c r="I43" s="16" t="n">
         <f aca="false">IF(AND(E43="",L43=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E43,$A$5:$A$47,0)),0),L43),1))</f>
-        <v>46468</v>
+        <v>46440</v>
       </c>
       <c r="J43" s="16" t="n">
         <f aca="false">WORKDAY(I43,D43-1)</f>
-        <v>46479</v>
+        <v>46451</v>
       </c>
       <c r="K43" s="13" t="n">
         <f aca="false">MATCH(C43,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2915,7 +2910,7 @@
       </c>
       <c r="L43" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2935,7 +2930,7 @@
         <v>37</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="G44" s="14" t="s">
         <v>162</v>
@@ -2945,11 +2940,11 @@
       </c>
       <c r="I44" s="16" t="n">
         <f aca="false">IF(AND(E44="",L44=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E44,$A$5:$A$47,0)),0),L44),1))</f>
-        <v>46468</v>
+        <v>46440</v>
       </c>
       <c r="J44" s="16" t="n">
         <f aca="false">WORKDAY(I44,D44-1)</f>
-        <v>46479</v>
+        <v>46451</v>
       </c>
       <c r="K44" s="13" t="n">
         <f aca="false">MATCH(C44,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2957,7 +2952,7 @@
       </c>
       <c r="L44" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2987,11 +2982,11 @@
       </c>
       <c r="I45" s="16" t="n">
         <f aca="false">IF(AND(E45="",L45=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E45,$A$5:$A$47,0)),0),L45),1))</f>
-        <v>46468</v>
+        <v>46440</v>
       </c>
       <c r="J45" s="16" t="n">
         <f aca="false">WORKDAY(I45,D45-1)</f>
-        <v>46479</v>
+        <v>46451</v>
       </c>
       <c r="K45" s="13" t="n">
         <f aca="false">MATCH(C45,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -2999,7 +2994,7 @@
       </c>
       <c r="L45" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3019,7 +3014,7 @@
         <v>40</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>168</v>
@@ -3029,11 +3024,11 @@
       </c>
       <c r="I46" s="16" t="n">
         <f aca="false">IF(AND(E46="",L46=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E46,$A$5:$A$47,0)),0),L46),1))</f>
-        <v>46482</v>
+        <v>46454</v>
       </c>
       <c r="J46" s="16" t="n">
         <f aca="false">WORKDAY(I46,D46-1)</f>
-        <v>46486</v>
+        <v>46458</v>
       </c>
       <c r="K46" s="13" t="n">
         <f aca="false">MATCH(C46,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -3041,7 +3036,7 @@
       </c>
       <c r="L46" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3061,7 +3056,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>171</v>
@@ -3071,11 +3066,11 @@
       </c>
       <c r="I47" s="16" t="n">
         <f aca="false">IF(AND(E47="",L47=0),$G$2,WORKDAY(MAX(IFERROR(INDEX($J$5:$J$47,MATCH(E47,$A$5:$A$47,0)),0),L47),1))</f>
-        <v>46482</v>
+        <v>46454</v>
       </c>
       <c r="J47" s="16" t="n">
         <f aca="false">WORKDAY(I47,D47-1)</f>
-        <v>46493</v>
+        <v>46465</v>
       </c>
       <c r="K47" s="13" t="n">
         <f aca="false">MATCH(C47,{"P0 - Foundation (M1)","P1 - Identity &amp; Data Protection (M2-3)","P2 - Detection &amp; Response (M4-6)","P3 - Cloud &amp; OT Security (M7-9)","P4 - Optimization &amp; Assurance (M10-12)"},0)</f>
@@ -3083,12 +3078,12 @@
       </c>
       <c r="L47" s="16" t="n">
         <f aca="false">MAX($J$31:$J$37)</f>
-        <v>46444</v>
+        <v>46416</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A1:W1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="I2:S2"/>
     <mergeCell ref="A3:B3"/>
@@ -3097,7 +3092,7 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="M5:X47">
+  <conditionalFormatting sqref="M5:W47">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND($K5=1,M$4&lt;=$J5,EOMONTH(M$4,0)&gt;=$I5)</formula>
     </cfRule>
